--- a/docs/research/provinces/SportsHub-British-Columbia.xlsx
+++ b/docs/research/provinces/SportsHub-British-Columbia.xlsx
@@ -11,12 +11,14 @@
     <sheet name="Leagues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Club-League Map" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Contacts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$230</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$199</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Club Sizes'!$A$1:$C$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -557,14 +559,11 @@
           <t>100 Mile House</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>eaglesbasketball.andrewsteeves@gmail.com</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Andrew Steeves — Basketball BC registry contact; founded by 'a local group of basketball enthusiasts', board of directors governs</t>
@@ -627,8 +626,6 @@
           <t>Abbotsford</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>info@abbotsfordbasketball.com</t>
@@ -701,7 +698,6 @@
           <t>Abbotsford</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>778-808-3198</t>
@@ -779,7 +775,6 @@
           <t>Abbotsford</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>778-859-6073</t>
@@ -800,14 +795,11 @@
           <t>John Tusi, Founder</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -845,7 +837,6 @@
           <t>Abbotsford</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>(778) 621-2004</t>
@@ -953,13 +944,11 @@
           <t>Prep/club basketball</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1027,13 +1016,11 @@
           <t>Weekly community youth basketball night</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1071,23 +1058,16 @@
           <t>Abbotsford</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>https://www.inspirebasketballclub.com</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -1135,7 +1115,6 @@
           <t>604-504-7441</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>https://gocascades.ca/sports/jr-cascades</t>
@@ -1151,13 +1130,11 @@
           <t>University of the Fraser Valley junior youth program</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1195,9 +1172,6 @@
           <t>Abbotsford</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>https://www.ktbpt.com</t>
@@ -1213,13 +1187,11 @@
           <t>Training</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1282,14 +1254,11 @@
           <t>Kyle Claggett, Founder/Head Coach Boys; Taylor Claggett, Founder/Head Coach Girls</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -1327,27 +1296,21 @@
           <t>Abbotsford</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>https://www.open-court.ca</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1390,7 +1353,6 @@
           <t>#27 - 22308 124 Ave, Maple Ridge, BC, V2X 0R6</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>revolutionbball@gmail.com</t>
@@ -1401,19 +1363,16 @@
           <t>https://www.revolutionbasketballclub.com</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Boys and girls club teams</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1451,23 +1410,16 @@
           <t>Abbotsford</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>https://www.sevenfoldbasketball.ca</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -1505,19 +1457,11 @@
           <t>Abbotsford</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -1555,9 +1499,6 @@
           <t>Burnaby</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>https://www.facebook.com/aimbball/</t>
@@ -1568,14 +1509,11 @@
           <t>Karis Ducharme, Co-founder</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -1643,13 +1581,11 @@
           <t>Camps</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -1697,7 +1633,6 @@
           <t>778-855-8273</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>https://burnabybasketballclub.com/</t>
@@ -1713,13 +1648,11 @@
           <t>Basketball school + rep elite teams grades 4-7 (3-4 practices/week); ages 10-18; tournaments in Vancouver and Seattle area, competitions across Canada/USA</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1762,7 +1695,6 @@
           <t>3700 Willingdon Ave, Burnaby, BC</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>info@fastbreakbasketball.org</t>
@@ -1773,15 +1705,11 @@
           <t>https://www.fastbreakbasketballbc.ca</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -1874,7 +1802,6 @@
           <t>https://g2athletics.com/</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1897,8 +1824,6 @@
           <t>Burnaby</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>info@northsideattack.com</t>
@@ -1919,13 +1844,11 @@
           <t>Elite club teams U10-U16 for Pitt Meadows/Maple Ridge; training programs</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>primary</t>
@@ -1963,8 +1886,6 @@
           <t>Burnaby</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>basketball.jennifercagampan@gmail.com</t>
@@ -2037,23 +1958,16 @@
           <t>Burnaby</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>http://www.triplethreatbasketball.ca</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -2091,7 +2005,6 @@
           <t>Campbell River</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>250-286-1161</t>
@@ -2169,7 +2082,6 @@
           <t>Castlegar</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>250-231-6682</t>
@@ -2195,13 +2107,11 @@
           <t>U15 boys travel team, U12/U14/U16 spring travel teams, youth skills development, JR J-Hawks ages 7–14</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>verified</t>
@@ -2239,7 +2149,6 @@
           <t>Castlegar</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>250-231-6682</t>
@@ -2275,7 +2184,6 @@
           <t>private program (with JSports apparel side-business)</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>verified</t>
@@ -2313,7 +2221,6 @@
           <t>Chilliwack</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>604-799-8035</t>
@@ -2349,7 +2256,6 @@
           <t>community nonprofit / league operator</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2417,13 +2323,11 @@
           <t>Club basketball</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>reported</t>
@@ -2461,7 +2365,6 @@
           <t>Chilliwack</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>604-702-8734</t>
@@ -2477,19 +2380,16 @@
           <t>http://tcathletics.ca/</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Basketball club teams, skills academy, mini ball (fall + spring); also volleyball (winter); 20+ years operating; tournament play across Canada and US</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>multi-sport org (nonprofit)</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2532,7 +2432,6 @@
           <t>Practices at Royal Bay Secondary School and other Westshore gyms</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>clubmanager@warriorsgirlsbasketball.ca</t>
@@ -2605,8 +2504,6 @@
           <t>Colwood/Langford (Westshore)</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>clubmanager@warriorsgirlsbasketball.ca</t>
@@ -2684,22 +2581,16 @@
           <t>Coombs Fairgrounds</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Free drop-in youth basketball ages 11-15 (Tuesday evenings), free 3-on-3 tournament during BC Youth Week; no club teams</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>multi-sport org (community recreation association)</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>reported</t>
@@ -2742,7 +2633,6 @@
           <t>2630 McLaughin Court, Coquitlam, BC V3B 6K4</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>bcswishbasketballclub@gmail.com</t>
@@ -2763,13 +2653,11 @@
           <t>Rep/club teams via fall prep &amp; tryouts, boys and girls; high-level coaching; serves Tri-Cities</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>verified</t>
@@ -2807,10 +2695,6 @@
           <t>Coquitlam</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Megan Weeks — Basketball BC registry contact</t>
@@ -2821,13 +2705,11 @@
           <t>Club basketball</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2890,14 +2772,11 @@
           <t>Doug Dowell, Founder and President</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>reported</t>
@@ -2935,7 +2814,6 @@
           <t>Coquitlam</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>(778) 858-6702</t>
@@ -2956,14 +2834,11 @@
           <t>Nishan Dhanoya, Founder</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -3001,27 +2876,21 @@
           <t>Coquitlam</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>https://tcnorthbasketball.com</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Camps and club teams for Coquitlam, Port Coquitlam, Port Moody, Pitt Meadows, Maple Ridge</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>reported</t>
@@ -3141,7 +3010,6 @@
           <t>Courtenay (Comox Valley)</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>(250) 334-7497</t>
@@ -3219,7 +3087,6 @@
           <t>Courtenay (Comox Valley)</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>250-338-9262 (coach) / 250-338-5371 (Courtenay Recreation)</t>
@@ -3302,7 +3169,6 @@
           <t>840 Shamrock Place</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>dimevalleybasketball@gmail.com</t>
@@ -3375,7 +3241,6 @@
           <t>Courtenay / Comox / Cumberland</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>250-702-3926</t>
@@ -3391,19 +3256,16 @@
           <t>https://c3basketball.ca/</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Boys basketball academy ages 8-15: fall Monday sessions (Gr 3-6 7-8pm, Gr 7-10 8-9pm), club teams, development camps</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>private academy (boys only)</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>reported</t>
@@ -3441,9 +3303,6 @@
           <t>Cranbrook</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>https://kanikkerz.wixsite.com/ekbasketballcamp</t>
@@ -3459,13 +3318,11 @@
           <t>Youth basketball camps; executives have coached in Cranbrook's Steve Nash league since ~2010</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>reported</t>
@@ -3503,8 +3360,6 @@
           <t>Dawson Creek</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>dcwildcatsbasketball@gmail.com</t>
@@ -3535,7 +3390,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>verified</t>
@@ -3573,7 +3427,6 @@
           <t>Delta (North Delta)</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>(672) 755-2121</t>
@@ -3651,8 +3504,6 @@
           <t>Delta (Tsawwassen/Ladner)</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>President@southdeltabasketball.org</t>
@@ -3725,8 +3576,6 @@
           <t>Duncan</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>sandeep@nextlevelbasketballacademy.ca</t>
@@ -3757,7 +3606,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3800,7 +3648,6 @@
           <t>Winter sessions at Queen Margaret's School, Duncan</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>beyondbasketballcvi@gmail.com</t>
@@ -3831,7 +3678,6 @@
           <t>community nonprofit (volunteer-run)</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3869,8 +3715,6 @@
           <t>Enderby (North Okanagan/Shuswap area)</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>ben@legacynorthacademy.com</t>
@@ -3891,13 +3735,11 @@
           <t>Beginner skills series, advanced clinics, traveling events, personal coaching, After Hours Hoops, Mindset 12 mental-performance program; first-time players to college-bound athletes</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3935,7 +3777,6 @@
           <t>Esquimalt</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>778-350-3241</t>
@@ -3986,7 +3827,6 @@
           <t>https://www.viccitybasketball.com/</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4009,8 +3849,6 @@
           <t>Fernie</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>fernieelevatebball@gmail.com</t>
@@ -4021,7 +3859,6 @@
           <t>https://www.ferniebasketball.com/</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Competitive youth development + club basketball program; spring club teams; hosts spring tournaments</t>
@@ -4037,7 +3874,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>reported</t>
@@ -4090,7 +3926,6 @@
           <t>erin.o'connor@nakazdliwhuten.ca</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Erin O'Conner, Recreation Coordinator</t>
@@ -4111,7 +3946,6 @@
           <t>First Nations community youth team</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -4149,8 +3983,6 @@
           <t>Fort St. John</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>info@fsjflight.ca</t>
@@ -4181,7 +4013,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>verified</t>
@@ -4219,8 +4050,6 @@
           <t>Fraser Valley (city not published)</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>jackiecraven7@gmail.com</t>
@@ -4241,13 +4070,11 @@
           <t>Club basketball</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4367,7 +4194,6 @@
           <t>Kamloops</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>778-384-0351</t>
@@ -4393,13 +4219,11 @@
           <t>Youth club teams Mini Ball through U16/U17 (boys &amp; girls, by age and gender), Elite Workout program, summer ProCamps, fall seasonal training</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4437,7 +4261,6 @@
           <t>Kamloops</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>250.819.4335</t>
@@ -4515,9 +4338,6 @@
           <t>Kamloops</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>https://kamloopskingscourt.leagueapps.com/</t>
@@ -4585,7 +4405,6 @@
           <t>Kamloops</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>250-319-4069</t>
@@ -4663,8 +4482,6 @@
           <t>Kelowna</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>dani@goodwinhoops.com</t>
@@ -4695,7 +4512,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>verified</t>
@@ -4733,8 +4549,6 @@
           <t>Kelowna</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>dani@goodwinhoops.com</t>
@@ -4765,7 +4579,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>verified</t>
@@ -4997,7 +4810,6 @@
           <t>8-week pre-season technical academy Gr6-7 and Gr8-9 (Sept–Nov), 1 or 2 sessions/week, $199–$299; coaches include UBCO Heat athletes</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -5045,7 +4857,6 @@
           <t>Kelowna</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>250-317-0321</t>
@@ -5071,7 +4882,6 @@
           <t>Small-group skills training, fundamentals focus, athleticism development; has coached club teams; elementary to high school ages</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -5119,7 +4929,6 @@
           <t>Kelowna (Okanagan location unpublished; HQ on North Shore/West Vancouver)</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>604-440-9224</t>
@@ -5145,7 +4954,6 @@
           <t>Girls-only development academy: club teams U10–U17 (Gr4–11), 'Okanagan — Spring Programs' plus North Shore programs, Elevate Her Retreat, athlete funding program</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -5198,7 +5006,6 @@
           <t>Operates out of Belmont Secondary, Spencer Middle School and John Stubbs school gyms</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>westshore.bball@gmail.com</t>
@@ -5276,22 +5083,16 @@
           <t>6450 199 St #62, Willoughby, Langley, BC V2Y 2X1</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>https://www.facebook.com/DDNationVentures</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -5329,8 +5130,6 @@
           <t>Langley</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>elevateyourgame.info@gmail.com</t>
@@ -5351,13 +5150,11 @@
           <t>Club teams U10-U17/18 boys &amp; girls (Langley + Surrey/South Surrey), Hoops Nights 10-week development, Rising Stars camps, shooting programs, private training</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5368,7 +5165,6 @@
           <t>https://elevateyourgame.ca/</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5391,13 +5187,11 @@
           <t>Langley</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>778-808-5170</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>https://www.impacthoops.ca/</t>
@@ -5423,7 +5217,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5434,7 +5227,6 @@
           <t>https://www.impacthoops.ca/</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5457,9 +5249,6 @@
           <t>Langley</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>https://www.jrbasketballclub.com</t>
@@ -5470,14 +5259,11 @@
           <t>Jaerok Shin, Founder/Coach (Coach J.R.)</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -5515,8 +5301,6 @@
           <t>Langley</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>admin@northlangleybasketball.ca</t>
@@ -5594,7 +5378,6 @@
           <t>20902 37A avenue, Langley, BC (Brookswood Secondary, practice location)</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>kstewart@sd35.bc.ca</t>
@@ -5605,7 +5388,6 @@
           <t>https://southlangleybasketball.com/</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>Stallions Youth Hoops rec (K-Gr7: K/1, Gr2/3, Gr4/5, Gr6/7), Stallions Champions League, Stallions Club Team (winter), Alice Brown Hoops, Super League (spring), camps</t>
@@ -5621,7 +5403,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5659,14 +5440,11 @@
           <t>Lower Mainland (Fraser River region — specific city not published)</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>brichlefty@gmail.com</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Bill Richards — Basketball BC registry contact</t>
@@ -5677,13 +5455,11 @@
           <t>Club basketball / academy</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5721,10 +5497,6 @@
           <t>Lower Mainland (Fraser River region — specific city not published)</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Bryan Lopez — Basketball BC registry contact</t>
@@ -5735,13 +5507,11 @@
           <t>Club basketball</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5779,14 +5549,11 @@
           <t>Lower Mainland (Fraser River/Fraser Valley/Vancouver-Coastal regions)</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>stephenrbeauchamp@gmail.com</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Steve Beauchamp — Basketball BC registry contact</t>
@@ -5797,13 +5564,11 @@
           <t>Club basketball across multiple regions</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5841,11 +5606,6 @@
           <t>Maple Ridge</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>Youth basketball (boys and girls)</t>
@@ -5861,7 +5621,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>reported</t>
@@ -5904,7 +5663,6 @@
           <t>#27 - 22308 124 Ave, Maple Ridge, BC, V2X 0R6</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>revolutionbball@gmail.com</t>
@@ -5915,19 +5673,16 @@
           <t>https://www.revolutionbasketballclub.com/</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>K-grade 12 youth programs, camps, Summer Elite Hoops, Fall Training Academy</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
           <t>community org</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>reported</t>
@@ -5965,27 +5720,21 @@
           <t>Merritt</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>https://www.facebook.com/p/Merritt-Youth-Basketball-Association-100054551556129/</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>Skill development sessions (~60 kids enrolled in first session per Merritt Herald)</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>reported</t>
@@ -6023,8 +5772,6 @@
           <t>Mission</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>info@missionbasketball.ca</t>
@@ -6035,7 +5782,6 @@
           <t>https://missionbasketball.ca/</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>Youth league ages 8-14, competitive club teams (spring/summer tryouts), summer camps and 3x3 league, Friday Night Basketball (fall), King of the Court 3x3 tournament; KidSport/JumpStart financial assistance</t>
@@ -6098,8 +5844,6 @@
           <t>Operates out of Nanaimo Christian School</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>https://www.believebasketballacademy.com/</t>
@@ -6125,7 +5869,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>primary</t>
@@ -6136,7 +5879,6 @@
           <t>https://www.believebasketballacademy.com/</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6159,14 +5901,11 @@
           <t>Nanaimo</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>chrisjoseph12@gmail.com</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Chris Joseph — Basketball BC registry contact (role not stated)</t>
@@ -6177,13 +5916,11 @@
           <t>Basketball BC member club (Vancouver Island-Central Coast region); programs not published online</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>rep/club program (structure not published)</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -6221,8 +5958,6 @@
           <t>Nanaimo</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>info@islandswish.com</t>
@@ -6325,7 +6060,6 @@
           <t>Basketball performance training grades 6-12 (junior Gr 6-8 / senior Gr 9-12 summer phases, strength/speed/injury-prevention focus); 2v2 basketball league is ages 17+ (adult)</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>private training facility (multi-sport, for-profit)</t>
@@ -6373,15 +6107,11 @@
           <t>Nanaimo</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>http://www.basketball.bc.ca/snyb-home</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>SNYB grassroots program (ages ~5–13) listed for Nanaimo in PacificSport VI's regional sport-organization directory</t>
@@ -6397,7 +6127,6 @@
           <t>community nonprofit (program)</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -6435,8 +6164,6 @@
           <t>Nelson</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>nelsonyouthbasketball@gmail.com</t>
@@ -6514,7 +6241,6 @@
           <t>Practices at New Westminster Secondary School</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>info@newwestbasketball.com</t>
@@ -6535,13 +6261,11 @@
           <t>Boys and girls club teams (incl. U13 girls expansion), 2 practices/week, ~6 tournaments/season; est. 2022, first club dedicated to New West</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>verified</t>
@@ -6579,23 +6303,16 @@
           <t>North Vancouver</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>https://3pointbasketball.com</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -6653,7 +6370,6 @@
           <t>https://www.3dbasketball.net</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>Academy training; co-powers the Canada West Hoops UA Next program with Vancouver Sports Club</t>
@@ -6669,7 +6385,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>reported</t>
@@ -6712,7 +6427,6 @@
           <t>1199 Lynn Valley Road</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>info@bcunitedbasketball.com</t>
@@ -6723,15 +6437,11 @@
           <t>https://www.bcunitedbasketball.com</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -6799,13 +6509,11 @@
           <t>Training</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>reported</t>
@@ -6925,15 +6633,11 @@
           <t>North Vancouver</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>https://nwsportsclub.ca/ballers-basketball</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>Girls &amp; boys ages 5-18; training 1-2x/week; club teams; league + tournament play; serves North &amp; West Vancouver</t>
@@ -6991,7 +6695,6 @@
           <t>North Vancouver</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>778-322-3529</t>
@@ -7007,19 +6710,16 @@
           <t>https://www.northshorebasketballacademy.com/</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>Camps, development leagues + programs, club teams; serves North &amp; West Vancouver; beginner to competitive</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>primary</t>
@@ -7030,7 +6730,6 @@
           <t>https://www.northshorebasketballacademy.com/</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7053,23 +6752,16 @@
           <t>North Vancouver</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>https://www.facebook.com/North-Vancouver-Basketball-Club-1401374406740781/</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -7127,7 +6819,6 @@
           <t>seymourbasketball.com</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>SNYB house league; plays at Parkgate Park area gyms</t>
@@ -7143,7 +6834,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -7181,8 +6871,6 @@
           <t>North Vancouver</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>splashbrothersbasketball1@gmail.com</t>
@@ -7193,15 +6881,11 @@
           <t>https://www.splashbballbc.com</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -7239,7 +6923,6 @@
           <t>North Vancouver</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>604-418-5986</t>
@@ -7260,14 +6943,11 @@
           <t>Kaiden Talib, Co-owner</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -7330,14 +7010,11 @@
           <t>Anthony Beyrouti, Founder/CEO</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -7430,7 +7107,6 @@
           <t>https://vancitybasketball.com/</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7453,9 +7129,6 @@
           <t>North Vancouver</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>https://www.wctraining.ca/</t>
@@ -7471,13 +7144,11 @@
           <t>Training</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
           <t>reported</t>
@@ -7515,8 +7186,6 @@
           <t>North Vancouver (per basketball604; Basketball BC registry lists it in Thompson-Okanagan)</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>Kaitlyn@newheightsbasketball.com</t>
@@ -7537,13 +7206,11 @@
           <t>Academy</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -7581,7 +7248,6 @@
           <t>Okanagan (multi-site; exact home city not published) + North Shore division</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>604-440-9224</t>
@@ -7607,13 +7273,11 @@
           <t>Girls-only competitive teams Grades K–12, Okanagan spring programs, North Shore spring programs, Elevate Her Retreat, athlete assistance/funding</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
           <t>verified</t>
@@ -7651,7 +7315,6 @@
           <t>Penticton</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>250-460-2230</t>
@@ -7729,14 +7392,11 @@
           <t>Penticton</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>jaiveer17@icloud.com</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Jaiveer Dhillon — Founder/coach (19 years old, founded as a player-turned-coach)</t>
@@ -7757,7 +7417,6 @@
           <t>community grassroots club</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
           <t>reported</t>
@@ -7800,26 +7459,21 @@
           <t>Pitt Meadows Recreation Centre (Tuesday sessions)</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>https://born2grindathletics.com/</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>Year-round weekly training sessions for youth</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
           <t>reported</t>
@@ -7830,7 +7484,6 @@
           <t>https://born2grindathletics.com/</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7853,8 +7506,6 @@
           <t>Pitt Meadows</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>nsattackathletics@gmail.com</t>
@@ -7865,19 +7516,16 @@
           <t>https://www.northsideattack.com/</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>Club season teams (tryouts), summer camps, skills development, community events; beginner through higher-level competitive</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
           <t>verified</t>
@@ -7915,21 +7563,16 @@
           <t>Port Alberni</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>https://www.albernibasketball.ca/</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>Community youth skills-development programs (e.g., 10-session youth spring program ~$100); umbrella org that has helped run local ladies' and men's leagues</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>community nonprofit</t>
@@ -7950,7 +7593,6 @@
           <t>https://www.albernibasketball.ca/</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7973,27 +7615,21 @@
           <t>Port Alberni</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>https://www.albernibasketball.ca/</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>Community youth basketball development in the Alberni Valley; youth spring program (2024); historically umbrella org for local ladies' and men's leagues; supports school 3-on-3 events Gr 4-7</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
           <t>reported</t>
@@ -8031,7 +7667,6 @@
           <t>Port Alberni</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>+1-250-257-0724</t>
@@ -8191,8 +7826,6 @@
           <t>Port Coquitlam</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>sassanrakhshani@yahoo.com</t>
@@ -8223,7 +7856,6 @@
           <t>multi-sport org</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
           <t>verified</t>
@@ -8286,14 +7918,11 @@
           <t>Doug Dowell, Founder and President</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -8331,15 +7960,11 @@
           <t>Powell River</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>http://www.basketball.bc.ca/snyb-home</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>SNYB grassroots program (ages ~5–13) listed for Powell River in PacificSport VI directory</t>
@@ -8355,7 +7980,6 @@
           <t>community nonprofit (program)</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -8393,7 +8017,6 @@
           <t>Prince George</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>250-960-5882</t>
@@ -8429,7 +8052,6 @@
           <t>university-affiliated youth club program</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
           <t>verified</t>
@@ -8467,8 +8089,6 @@
           <t>Prince George</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>pgminorbasketball@gmail.com</t>
@@ -8541,8 +8161,6 @@
           <t>Prince George (HQ) + Kamloops division</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>hoops@northernbounce.com</t>
@@ -8573,7 +8191,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
           <t>verified</t>
@@ -8641,13 +8258,11 @@
           <t>Youth basketball program (details not published)</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
           <t>primary</t>
@@ -8685,23 +8300,16 @@
           <t>Quesnel</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Sean Cunningham — Basketball BC registry contact</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
           <t>primary</t>
@@ -8779,7 +8387,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
           <t>primary</t>
@@ -8817,23 +8424,16 @@
           <t>Richmond</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>Girls basketball</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -8871,8 +8471,6 @@
           <t>Richmond</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>cmntyelite@gmail.com</t>
@@ -8883,13 +8481,11 @@
           <t>https://www.community-elite.com/</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>Fall club teams U11-U16, summer camps (Young Hoopers U11-U13, Grind Hour U13-U17); mission of removing financial barriers</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -8937,8 +8533,6 @@
           <t>Richmond</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>landondy_11@yahoo.com</t>
@@ -8954,14 +8548,11 @@
           <t>Landon Dy</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -8999,9 +8590,6 @@
           <t>Richmond</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>https://meccasports.ca</t>
@@ -9017,13 +8605,11 @@
           <t>Youth basketball programs (details behind 403 during sweep)</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
           <t>reported</t>
@@ -9066,7 +8652,6 @@
           <t>2251 No. 5 Road, Richmond, BC V6X 2S8</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
           <t>playmakersbballtraining@gmail.com</t>
@@ -9077,15 +8662,11 @@
           <t>https://playmakersbball.com</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -9128,22 +8709,16 @@
           <t>St Joseph the Worker Parish</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>https://www.richmondsportsacademy.com</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -9273,21 +8848,16 @@
           <t>604-347-5151</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>https://www.facebook.com/ShootingStarsBall/</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -9330,7 +8900,6 @@
           <t>9180 No. 1 Rd.</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>WRSummerslam@Richmond.ca</t>
@@ -9341,7 +8910,6 @@
           <t>https://www.westrichmondsummerslam.com/</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>Non-profit recreational summer basketball program run by West Richmond Community Association since 2003; 385+ participants (2024)</t>
@@ -9357,7 +8925,6 @@
           <t>community nonprofit (community association program)</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
           <t>reported</t>
@@ -9395,8 +8962,6 @@
           <t>Saanich (Royal Oak)</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
           <t>rebelsrebelles@gmail.com</t>
@@ -9474,14 +9039,11 @@
           <t>Practices at Bayside Middle School and North Saanich Middle School</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>https://www.saanichpeninsulabasketball.com/</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>Night League teams boys &amp; girls ages 8-17 (Sept-Mar, weekly practice + game in Victoria); Little Dribblers intro program (via Panorama Recreation); summer camps 2026</t>
@@ -9539,8 +9101,6 @@
           <t>Salmon Arm</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
           <t>shuswaphoops2023@gmail.com</t>
@@ -9618,7 +9178,6 @@
           <t>Programs at GISS (Gulf Islands Secondary School) gym</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>saltspringbasketball@gmail.com</t>
@@ -9639,13 +9198,11 @@
           <t>Formed 2024; development programs boys &amp; girls grades 5-12; 3-on-3 tournaments; pick-up and all-ages events; members get Basketball BC membership/insurance and KidSport funding access up to $400/athlete</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
           <t>verified</t>
@@ -9683,8 +9240,6 @@
           <t>Smithers</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>clubbasketballbv@gmail.com</t>
@@ -9715,7 +9270,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
           <t>verified</t>
@@ -9753,15 +9307,11 @@
           <t>Sooke</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
           <t>https://www.sookebasketballclub.com/</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>Established 1996: grades 3–5 house league (4 teams of ~10), club teams (U9 girls, U17 girls, U13/U15/U17 boys), youth camps</t>
@@ -9792,7 +9342,6 @@
           <t>https://www.sookebasketballclub.com/</t>
         </is>
       </c>
-      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9825,13 +9374,11 @@
           <t>604-907-2024</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
           <t>https://hustlebasketball.ca/</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>Youth training and club programs for all levels across Squamish, Whistler, Pemberton; formed from merger of Squamish Youth Basketball Association (est. 2018, 200+ players) and Hoop Reel Basketball Academy</t>
@@ -9889,8 +9436,6 @@
           <t>Squamish</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>info@hoopreel.com</t>
@@ -9921,7 +9466,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
           <t>reported</t>
@@ -9964,7 +9508,6 @@
           <t>15358 67 Ave, Surrey, BC V3S 6C7</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>info@athelitebasketball.com</t>
@@ -9980,14 +9523,11 @@
           <t>Aman Heran</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -10035,13 +9575,11 @@
           <t>778-591-3660</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>http://www.bcprep.com</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>Prep academy plus youth basketball league</t>
@@ -10057,7 +9595,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
           <t>primary</t>
@@ -10115,7 +9652,6 @@
           <t>https://bcprep.com/</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>BCPrep Basketball Youth League grades 3-10 (boys &amp; girls, 4 tiers: White/Orange/Black/Grey), high-performance training, strength training, soccer academies, tutoring</t>
@@ -10146,7 +9682,6 @@
           <t>https://bcprep.com/programs/basketball-youth-league/</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10179,7 +9714,6 @@
           <t>604-670-4340</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
           <t>https://drivebasketball.com/</t>
@@ -10287,7 +9821,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
           <t>reported</t>
@@ -10330,8 +9863,6 @@
           <t>#120 17828 65A Ave, Surrey, BC V3S 1Z3</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>https://www.ekhoopstraining.com</t>
@@ -10347,13 +9878,11 @@
           <t>Training</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
           <t>reported</t>
@@ -10391,14 +9920,11 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>reid_g@surreyschools.ca</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Greg Reid — Basketball BC registry contact</t>
@@ -10409,13 +9935,11 @@
           <t>Club basketball</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
           <t>primary</t>
@@ -10483,13 +10007,11 @@
           <t>Youth basketball programs</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
           <t>reported</t>
@@ -10527,10 +10049,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>Elliot Mason, Head Coach</t>
@@ -10541,13 +10059,11 @@
           <t>Youth club team programs, private training (head coach Elliot Mason per third-party listing)</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -10585,19 +10101,11 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -10655,15 +10163,11 @@
           <t>https://sites.google.com/site/fvbasketball/</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -10701,15 +10205,11 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>https://www.fundamentalsbc.com/</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>Club teams U9-U17 boys, Developmental Basketball League gr3-5, Little Dribblers ages 5-7 coed, private training; locations Surrey, White Rock, Burnaby</t>
@@ -10725,7 +10225,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
           <t>primary</t>
@@ -10768,26 +10267,21 @@
           <t>17475 59 Ave, Surrey, BC V3S 1P3</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
           <t>https://www.fundamentalsbc.com/</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>Youth development programs and training; operating since summer 2020</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
           <t>primary</t>
@@ -10825,9 +10319,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>https://l2gbasketball.ca</t>
@@ -10838,14 +10329,11 @@
           <t>Jun Labrador, Founder/Coach</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -10888,7 +10376,6 @@
           <t>17665 66A Ave Unit 101, Surrey, BC V3S 7X1</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
           <t>info@nextgenerationathletics.ca</t>
@@ -10909,13 +10396,11 @@
           <t>GEN94 club team ages 10-17, all-access group training, Rising Star ages 6-9, girls elite training, 1-on-1 development, summer camps</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
           <t>primary</t>
@@ -10953,7 +10438,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>778-859-2372</t>
@@ -10989,7 +10473,6 @@
           <t>community nonprofit / league operator</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
           <t>verified</t>
@@ -11027,19 +10510,11 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -11077,23 +10552,16 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
           <t>https://www.riseupball.com</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -11136,26 +10604,21 @@
           <t>15550 99A Ave</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>https://www.rookiessc.ca</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>Youth basketball club</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -11223,13 +10686,11 @@
           <t>Club basketball</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
           <t>primary</t>
@@ -11287,15 +10748,11 @@
           <t>https://www.showtimeacademy.net</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -11333,9 +10790,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
           <t>https://www.facebook.com/slammajammabasketball/</t>
@@ -11351,13 +10805,11 @@
           <t>Girls basketball club, grades 5-7 (U13 Future Crusaders teams); linked to Catholic elementary schools (Star of the Sea, St. Matthew's)</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
           <t>reported</t>
@@ -11395,7 +10847,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>778-229-4533</t>
@@ -11411,15 +10862,11 @@
           <t>https://www.facebook.com/spottersbball</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -11457,14 +10904,11 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
           <t>Bsingh.aloha@outlook.com</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>Bob Singh — Basketball BC registry contact</t>
@@ -11475,13 +10919,11 @@
           <t>Club basketball</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
           <t>primary</t>
@@ -11519,8 +10961,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
           <t>info.surreyrebelsbasketball@gmail.com</t>
@@ -11531,19 +10971,16 @@
           <t>https://www.surreyrebelsbasketball.com/</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>Boys and girls competitive/travel teams; NCAA-certified; competing in US west-coast NCAA tournaments since 2014</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr">
         <is>
           <t>primary</t>
@@ -11581,7 +11018,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>778-386-4288</t>
@@ -11659,19 +11095,11 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -11714,7 +11142,6 @@
           <t>Clubhouse: 17358 104a Ave, Unit 1, Surrey, BC V4N 5M3; PO Box #409, 15940 Fraser Hwy, Surrey, BC V4N 9E9</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>info@vancouversportsclub.ca</t>
@@ -11792,7 +11219,6 @@
           <t>17358 104A Avenue, Unit 1, Surrey, BC</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
           <t>info@westcoastbasketball.com</t>
@@ -11803,15 +11229,11 @@
           <t>https://www.westcoastbasketball.com</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
           <t>reported</t>
@@ -11874,14 +11296,11 @@
           <t>Harleen Dulay, Director &amp; Co-Founder</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -11919,8 +11338,6 @@
           <t>Surrey (South Surrey / White Rock)</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
           <t>elevateyourgame.info@gmail.com</t>
@@ -11941,13 +11358,11 @@
           <t>Club teams U10-U17/18 boys &amp; girls, fall/winter/spring seasons</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr">
         <is>
           <t>primary</t>
@@ -11995,7 +11410,6 @@
           <t>250-635-6531 ext 8017</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
           <t>https://www.terrace.ca/parks-recreation/sports-clubs</t>
@@ -12011,13 +11425,11 @@
           <t>Friday-evening youth basketball at Caledonia Secondary gym</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr">
         <is>
           <t>reported</t>
@@ -12055,19 +11467,11 @@
           <t>Unknown (Fraser River region — Surrey/Delta/Richmond/New West)</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -12105,19 +11509,11 @@
           <t>Unknown (Fraser River region — Surrey/Delta/Richmond/New West)</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -12155,19 +11551,11 @@
           <t>Unknown (Fraser Valley)</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -12205,13 +11593,11 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>778.835.3632</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
           <t>https://www.academybasketball.com</t>
@@ -12237,7 +11623,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr">
         <is>
           <t>reported</t>
@@ -12275,8 +11660,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
           <t>cmntyelite@gmail.com</t>
@@ -12297,13 +11680,11 @@
           <t>Club basketball</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12366,14 +11747,11 @@
           <t>Nap Santos — Co-Founder (also head coach, St. Patrick's Secondary varsity)</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr">
         <is>
           <t>reported</t>
@@ -12411,9 +11789,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
           <t>https://www.dynamitebasketball.com</t>
@@ -12424,14 +11799,11 @@
           <t>Brodan Thiel — Co-Founder; Louis Johnson — Co-Founder</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr">
         <is>
           <t>reported</t>
@@ -12474,7 +11846,6 @@
           <t>BCIT Recreation Centre, Burnaby/Vancouver, BC (West-location training venue; no street address published)</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
           <t>coaches@formbasketball.com</t>
@@ -12490,14 +11861,11 @@
           <t>Paul Ekeocha — Founder &amp; President (BBB profile lists him as Owner)</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr">
         <is>
           <t>reported</t>
@@ -12535,8 +11903,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
           <t>team@finishstrongbasketball.ca</t>
@@ -12552,14 +11918,11 @@
           <t>David Knight — Founder &amp; Head Coach</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr">
         <is>
           <t>reported</t>
@@ -12597,8 +11960,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
           <t>futurebouncebasketball@gmail.com</t>
@@ -12614,14 +11975,11 @@
           <t>Phoebe Lee — Head Coach</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr">
         <is>
           <t>reported</t>
@@ -12659,14 +12017,11 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
           <t>rpennington.basketball@gmail.com</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>Rodney Pennington — Basketball BC registry contact</t>
@@ -12677,13 +12032,11 @@
           <t>Skills academy</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12721,7 +12074,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>604-834-4880</t>
@@ -12742,14 +12094,11 @@
           <t>Doug Plumb — Owner/Founder</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr">
         <is>
           <t>reported</t>
@@ -12787,8 +12136,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
           <t>journeybasketball2020@gmail.com</t>
@@ -12804,14 +12151,11 @@
           <t>Derick Gonzales — Head Coach</t>
         </is>
       </c>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr">
         <is>
           <t>reported</t>
@@ -12849,7 +12193,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>604-258-8390</t>
@@ -12875,13 +12218,11 @@
           <t>Youth basketball programs</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12944,14 +12285,11 @@
           <t>Jessie Bay (Founder)</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -13009,19 +12347,16 @@
           <t>https://ysbc.bms-1.com</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>Kids basketball programs at UBC</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr">
         <is>
           <t>reported</t>
@@ -13059,23 +12394,16 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
           <t>https://www.facebook.com/MoreHeartBasketball/</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -13118,7 +12446,6 @@
           <t>1 Kingsway, Vancouver, BC V5T 3H7 (CRA registered-charity address)</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
           <t>info@nighthoops.ca</t>
@@ -13149,7 +12476,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr">
         <is>
           <t>verified</t>
@@ -13187,9 +12513,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
           <t>https://www.instagram.com/pursuitsportsclub/</t>
@@ -13200,14 +12523,11 @@
           <t>Warren Liang (Founder)</t>
         </is>
       </c>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -13245,7 +12565,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>236-889-1585</t>
@@ -13363,7 +12682,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr">
         <is>
           <t>verified</t>
@@ -13401,7 +12719,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>604-723-1582</t>
@@ -13427,13 +12744,11 @@
           <t>Skills training</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr">
         <is>
           <t>reported</t>
@@ -13471,7 +12786,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>604-626-6322</t>
@@ -13579,13 +12893,11 @@
           <t>Community basketball program (Strathcona neighbourhood)</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -13623,7 +12935,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>778-387-4543</t>
@@ -13644,14 +12955,11 @@
           <t>Nap Santos — Head Coach</t>
         </is>
       </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -13694,7 +13002,6 @@
           <t>530 East 41st Avenue, Vancouver, BC V5W 1P3 (John Oliver Secondary; gym access via St. George St entrance)</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
           <t>vancouveracesbballclub@gmail.com</t>
@@ -13710,14 +13017,11 @@
           <t>Arthur Fong, Pat Lee, Tiffani Martinez, Phina Tu — Directors (no single president named; Pat Lee handles registration/website/VSSAA liaison)</t>
         </is>
       </c>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr">
         <is>
           <t>reported</t>
@@ -13775,7 +13079,6 @@
           <t>https://vancouvereagles.com/</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
           <t>Weekly programs ages 6-8/9-11/12-15, summer camps, performance training; 350+ players/season, 20+ years operating</t>
@@ -13838,7 +13141,6 @@
           <t>1001 Cotton Drive, Vancouver, BC V5L 3T4 (Britannia Secondary School, Gyms A &amp; B)</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
           <t>info@vgba.ca</t>
@@ -13869,7 +13171,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr">
         <is>
           <t>verified</t>
@@ -13937,13 +13238,11 @@
           <t>Club teams</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr">
         <is>
           <t>reported</t>
@@ -14021,7 +13320,6 @@
           <t>multi-sport org / league operator</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr">
         <is>
           <t>reported</t>
@@ -14141,8 +13439,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
           <t>yuvasc2018@gmail.com</t>
@@ -14153,15 +13449,11 @@
           <t>https://www.facebook.com/vancitysc/</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -14199,9 +13491,6 @@
           <t>Vancouver Island (city unconfirmed)</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
           <t>https://smithperformancebasketball.com/</t>
@@ -14217,13 +13506,11 @@
           <t>Youth skills and player-development group (practice/training/play development for all levels)</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
           <t>private academy (training group)</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -14261,14 +13548,11 @@
           <t>Vancouver Island (city unconfirmed)</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
           <t>thewatchmanacademymentorship@gmail.com</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>Ayodeji Ipaye — Basketball BC registry contact (role not stated)</t>
@@ -14279,13 +13563,11 @@
           <t>Basketball BC member club (Vancouver Island-Central Coast region); programs not published online</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
           <t>private academy (mentorship-branded; inferred from name/email)</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -14323,13 +13605,11 @@
           <t>Vernon</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
           <t>(778) 240-5370</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
           <t>https://acehoops.net/</t>
@@ -14355,7 +13635,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr">
         <is>
           <t>primary</t>
@@ -14393,23 +13672,16 @@
           <t>Vernon</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
           <t>https://www.nlbasketball.ca/</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -14447,7 +13719,6 @@
           <t>Vernon</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
           <t>250-540-5075</t>
@@ -14473,7 +13744,6 @@
           <t>Spring academy Gr2–10 at Hillview &amp; Harwood Elementary and Vernon Christian School, summer camps boys Gr4–10, personal training academy ($150/mo)</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -14521,8 +13791,6 @@
           <t>Vernon</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
           <t>tayahoops@gmail.com</t>
@@ -14543,13 +13811,11 @@
           <t>Independent elite training: fundamentals, pro-level drills, film study, individualized feedback and mentorship for Vernon youth</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr">
         <is>
           <t>primary</t>
@@ -14587,9 +13853,6 @@
           <t>Vernon</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
           <t>https://www.facebook.com/vernonminorbasketball/</t>
@@ -14667,7 +13930,6 @@
           <t>1-677-124-44227</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr">
         <is>
           <t>https://www.fyba.ca/</t>
@@ -14693,7 +13955,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr">
         <is>
           <t>primary</t>
@@ -14736,8 +13997,6 @@
           <t>St. James Elementary School, 2700 28th Ave, Vernon, BC V1T 1V7</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr">
         <is>
           <t>https://www.rootssportsclub.ca/</t>
@@ -14753,7 +14012,6 @@
           <t>Local basketball evenings for school-aged kids in Vernon and Lake Country, July camp, team camp, Mini Hoopers summer camp, skills development</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -14801,11 +14059,6 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
           <t>Registers youth teams in the Victoria night league (details not published)</t>
@@ -14821,7 +14074,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr">
         <is>
           <t>reported</t>
@@ -14864,7 +14116,6 @@
           <t>Assessments/practices at Lansdowne Middle School, 1765 Lansdowne Rd, Victoria</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
           <t>carnarvonvpbasketball@gmail.com</t>
@@ -14947,7 +14198,6 @@
           <t>(250) 592-4038</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
         <is>
           <t>https://www.elipasquale.com/</t>
@@ -14973,7 +14223,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr">
         <is>
           <t>reported</t>
@@ -15016,7 +14265,6 @@
           <t>St. Margaret's School, 1080 Lucas Avenue</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
           <t>Info@flightbasketball.ca</t>
@@ -15089,8 +14337,6 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
           <t>academy@gryphonsbasketball.net</t>
@@ -15101,7 +14347,6 @@
           <t>https://www.gryphonsbasketball.net</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>Registers youth teams in the Victoria night league (details not published)</t>
@@ -15117,7 +14362,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -15165,7 +14409,6 @@
           <t>(250) 999-9380</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
         <is>
           <t>https://www.jumpshotbasketball.org/</t>
@@ -15233,8 +14476,6 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
           <t>hello@rexsports.ca</t>
@@ -15307,9 +14548,6 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr">
         <is>
           <t>https://svibasketball.com/</t>
@@ -15417,7 +14655,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr">
         <is>
           <t>primary</t>
@@ -15455,9 +14692,6 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr">
         <is>
           <t>https://playsport.com/thundernationbasketball_ag_cf54630b</t>
@@ -15525,8 +14759,6 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr">
         <is>
           <t>viccityhoops@gmail.com</t>
@@ -15557,7 +14789,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr">
         <is>
           <t>reported</t>
@@ -15600,7 +14831,6 @@
           <t>2970 Jutland Road, Victoria, BC V8T 5K2 (primary practice: Selkirk Montessori School)</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
           <t>office@vichowlers.ca</t>
@@ -15611,7 +14841,6 @@
           <t>https://vichowlers.ca/</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>Boys U11 (Gr 3-5) and U13 (Gr 6-7) teams; season Sept-Feb/Mar, 1 practice + 1 game weekly</t>
@@ -15627,7 +14856,6 @@
           <t>community club (nonprofit status not stated)</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr">
         <is>
           <t>primary</t>
@@ -15638,7 +14866,6 @@
           <t>https://vichowlers.ca/</t>
         </is>
       </c>
-      <c r="P223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -15666,7 +14893,6 @@
           <t>McKinnon Gym, University of Victoria</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
           <t>cve@uvic.ca</t>
@@ -15687,7 +14913,6 @@
           <t>Vikes Elite tryout teams boys U12-U15 and U16-U17, Vikes Elite 3x3 Winter Academy, U11 spring skills ($200), high-performance programs 13-18, camps, hosts Vikes Nation Shootout tournament</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
           <t>multi-sport org (university recreation program)</t>
@@ -15735,7 +14960,6 @@
           <t>Victoria (Oak Bay)</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
           <t>866-422-7310</t>
@@ -15771,7 +14995,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr">
         <is>
           <t>primary</t>
@@ -15809,8 +15032,6 @@
           <t>West Kelowna</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
           <t>westkhoops@gmail.com</t>
@@ -15841,7 +15062,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr">
         <is>
           <t>verified</t>
@@ -15909,13 +15129,11 @@
           <t>Spring programs grades 2-9 (co-ed and gender-specific), summer camps</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr">
         <is>
           <t>verified</t>
@@ -15953,15 +15171,11 @@
           <t>Whistler</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
         <is>
           <t>https://www.whistleryouthbasketball.com/</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>Summer training and private coaching</t>
@@ -15977,7 +15191,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -16015,10 +15228,6 @@
           <t>Williams Lake</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
           <t>Jeremy LaBelle — head coach</t>
@@ -16029,13 +15238,11 @@
           <t>U18 male AAU-style team drawing players from across the BC Interior (incl. 100 Mile House); gives Interior HS players post-season/post-grad competitive opportunity</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr">
         <is>
           <t>reported</t>
@@ -16073,7 +15280,6 @@
           <t>Williams Lake</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>(250) 267-4282</t>
@@ -16262,7 +15468,6 @@
           <t>Fall: Sep-Nov; Winter: select Sundays early Nov through championship finals weekend late Feb</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>davidjaymunro@gmail.com; tournament entries from $289; no admission charged at events</t>
@@ -16320,8 +15525,6 @@
           <t>Oct-Mar; 2026-27 season starts Oct 13, 2026; team registration after September AGM, player registration/transfer deadline Nov 15</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>verified</t>
@@ -16426,7 +15629,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Fall/winter and spring league sessions plus holiday camps</t>
@@ -16484,13 +15686,11 @@
           <t>Richmond</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Fall/winter house league; rep teams play other Lower Mainland competitive teams</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>rybl@richmond.ca; +1 778-928-7925; 8880 Williams Road, Richmond BC</t>
@@ -16538,14 +15738,11 @@
           <t>Greater Vancouver incl. Surrey/Delta communities</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Sessions incl. Spring (Apr-Jun, registration opens Jan 11); practices Tue/Wed, games Fri evenings</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>primary</t>
@@ -16588,13 +15785,11 @@
           <t>North Vancouver &amp; West Vancouver</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Fall/winter school-year season</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>admin@delbrookbasketball.com; PO Box 805, 1641 Lonsdale Ave, North Vancouver BC V7M 2J5</t>
@@ -16642,7 +15837,6 @@
           <t>North Vancouver (Seymour)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Fall/winter school-year season</t>
@@ -16715,7 +15909,6 @@
           <t>TeamLinkt (registration app.teamlinkt.com/register/go/southburnabybasketball) AND LeagueApps (sbmcbasketball.leagueapps.com for spring boys club program)</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>verified</t>
@@ -16830,8 +16023,6 @@
           <t>Fall/Winter late Sep-early Mar; Spring season late Mar-Jun</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>primary</t>
@@ -16874,10 +16065,6 @@
           <t>North Delta</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>reported</t>
@@ -16920,7 +16107,6 @@
           <t>Kelowna + West Kelowna</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Fall program 8 weeks + playoff week (grades 6+); also spring programming; weeknight-only 5-9:30pm; fees $225-$350/session</t>
@@ -16978,14 +16164,11 @@
           <t>Prince George</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>2025-26 school-year season (registration open)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>primary</t>
@@ -17028,14 +16211,11 @@
           <t>Kamloops</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Jan-Mar; registration opens late Oct</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>primary</t>
@@ -17088,8 +16268,6 @@
           <t>Annual, March (Mar 15-20, 2026)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>verified</t>
@@ -17147,7 +16325,6 @@
           <t>Exposure Events (basketball.exposureevents.com) + own mobile app</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>verified</t>
@@ -17190,7 +16367,6 @@
           <t>Surrey, Delta + satellites in Vancouver, Coquitlam, White Rock</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Spring season Apr-Jun; club tournaments year-round; summer camps</t>
@@ -17201,7 +16377,6 @@
           <t>Hoopsoles Events App for league schedules/standings/scores</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>primary</t>
@@ -17244,14 +16419,11 @@
           <t>Vancouver Island (Victoria, Duncan, Nanaimo, Courtenay rotation)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Spring leagues; Island Summer Shootout late May; VI Club Championship + Canadian Summer Tipoff late June</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>primary</t>
@@ -17309,7 +16481,6 @@
           <t>RecLeague.net (U12 Winter League listing)</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>primary</t>
@@ -17352,9 +16523,6 @@
           <t>North Surrey</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>nsbasketballclub@gmail.com; (778) 859-2372</t>
@@ -17402,10 +16570,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>primary</t>
@@ -17448,14 +16612,11 @@
           <t>Kelowna / Central Okanagan</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Main club season April-early March, tryouts in February</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>primary</t>
@@ -17498,10 +16659,6 @@
           <t>West Kelowna</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>verified</t>
@@ -17544,10 +16701,6 @@
           <t>Nanaimo / Central Vancouver Island</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>primary</t>
@@ -17590,10 +16743,6 @@
           <t>Nanaimo</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>reported</t>
@@ -17636,10 +16785,6 @@
           <t>Courtenay / Comox / Cumberland</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>primary</t>
@@ -17682,14 +16827,11 @@
           <t>Vernon</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>eSportsDesk (esportsdesk.com clientID 5889)</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>primary</t>
@@ -17732,10 +16874,6 @@
           <t>Chilliwack</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>reported</t>
@@ -17778,16 +16916,11 @@
           <t>Maple Ridge</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -17820,16 +16953,11 @@
           <t>Squamish</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -17862,16 +16990,11 @@
           <t>Whistler</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -17904,14 +17027,11 @@
           <t>BC teams travelling to circuit events (US/Canada)</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Spring/Summer</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>verified</t>
@@ -22988,7 +22108,6 @@
           <t>100 Mile House</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>eaglesbasketball.andrewsteeves@gmail.com</t>
@@ -22999,7 +22118,6 @@
           <t>Andrew Steeves — Basketball BC registry contact; founded by 'a local group of basketball enthusiasts', board of directors governs</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23012,7 +22130,6 @@
           <t>Abbotsford</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>info@abbotsfordbasketball.com</t>
@@ -23205,7 +22322,6 @@
           <t>604-504-7441</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Run by UFV Cascades athletics department</t>
@@ -23228,8 +22344,6 @@
           <t>Abbotsford</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Kabir Dhaliwal, Founder</t>
@@ -23284,13 +22398,11 @@
           <t>Abbotsford</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>revolutionbball@gmail.com</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>https://www.revolutionbasketballclub.com</t>
@@ -23308,8 +22420,6 @@
           <t>Burnaby</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Karis Ducharme, Co-founder</t>
@@ -23369,7 +22479,6 @@
           <t>778-855-8273</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Dragan Kisin — founder/head coach</t>
@@ -23392,13 +22501,11 @@
           <t>Burnaby</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>info@fastbreakbasketball.org</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>https://www.fastbreakbasketballbc.ca</t>
@@ -23448,7 +22555,6 @@
           <t>Burnaby</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>info@northsideattack.com</t>
@@ -23476,7 +22582,6 @@
           <t>Burnaby</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>basketball.jennifercagampan@gmail.com</t>
@@ -23674,7 +22779,6 @@
           <t>info@tcathletics.ca</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>http://tcathletics.ca/</t>
@@ -23692,7 +22796,6 @@
           <t>Colwood (Westshore)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>clubmanager@warriorsgirlsbasketball.ca</t>
@@ -23720,7 +22823,6 @@
           <t>Colwood/Langford (Westshore)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>clubmanager@warriorsgirlsbasketball.ca</t>
@@ -23748,7 +22850,6 @@
           <t>Coquitlam</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>bcswishbasketballclub@gmail.com</t>
@@ -23776,14 +22877,11 @@
           <t>Coquitlam</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Megan Weeks — Basketball BC registry contact</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -23956,7 +23054,6 @@
           <t>Courtenay (Comox Valley; also serves Campbell River, Oceanside, Powell River)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>dimevalleybasketball@gmail.com</t>
@@ -23994,7 +23091,6 @@
           <t>info@c3basketball.ca</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>https://c3basketball.ca/</t>
@@ -24012,8 +23108,6 @@
           <t>Cranbrook</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Garold Gipman and Kieren Britton — executives/coaches</t>
@@ -24036,7 +23130,6 @@
           <t>Dawson Creek</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>dcwildcatsbasketball@gmail.com</t>
@@ -24096,7 +23189,6 @@
           <t>Delta (Tsawwassen/Ladner)</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>President@southdeltabasketball.org</t>
@@ -24124,7 +23216,6 @@
           <t>Duncan</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>sandeep@nextlevelbasketballacademy.ca</t>
@@ -24152,7 +23243,6 @@
           <t>Duncan (Cowichan Valley)</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>beyondbasketballcvi@gmail.com</t>
@@ -24180,7 +23270,6 @@
           <t>Enderby (North Okanagan/Shuswap area)</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>ben@legacynorthacademy.com</t>
@@ -24240,13 +23329,11 @@
           <t>Fernie</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>fernieelevatebball@gmail.com</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>https://www.ferniebasketball.com/</t>
@@ -24279,7 +23366,6 @@
           <t>Erin O'Conner, Recreation Coordinator</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -24292,7 +23378,6 @@
           <t>Fort St. John</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>info@fsjflight.ca</t>
@@ -24320,7 +23405,6 @@
           <t>Fraser Valley (city not published)</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>jackiecraven7@gmail.com</t>
@@ -24444,8 +23528,6 @@
           <t>Kamloops</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Ryan Porter — Founder (former UCC Sun Demons player; founded 2019)</t>
@@ -24500,7 +23582,6 @@
           <t>Kelowna</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>dani@goodwinhoops.com</t>
@@ -24528,7 +23609,6 @@
           <t>Kelowna</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>dani@goodwinhoops.com</t>
@@ -24716,7 +23796,6 @@
           <t>Langford</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>westshore.bball@gmail.com</t>
@@ -24744,7 +23823,6 @@
           <t>Langley</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>elevateyourgame.info@gmail.com</t>
@@ -24777,7 +23855,6 @@
           <t>778-808-5170</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Jon Schmidt — director</t>
@@ -24800,8 +23877,6 @@
           <t>Langley</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Jaerok Shin, Founder/Coach (Coach J.R.)</t>
@@ -24824,7 +23899,6 @@
           <t>Langley</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>admin@northlangleybasketball.ca</t>
@@ -24852,13 +23926,11 @@
           <t>Langley</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>kstewart@sd35.bc.ca</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>https://southlangleybasketball.com/</t>
@@ -24876,7 +23948,6 @@
           <t>Lower Mainland (Fraser River region — specific city not published)</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>brichlefty@gmail.com</t>
@@ -24887,7 +23958,6 @@
           <t>Bill Richards — Basketball BC registry contact</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -24900,14 +23970,11 @@
           <t>Lower Mainland (Fraser River region — specific city not published)</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Bryan Lopez — Basketball BC registry contact</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -24920,7 +23987,6 @@
           <t>Lower Mainland (Fraser River/Fraser Valley/Vancouver-Coastal regions)</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>stephenrbeauchamp@gmail.com</t>
@@ -24931,7 +23997,6 @@
           <t>Steve Beauchamp — Basketball BC registry contact</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -24944,13 +24009,11 @@
           <t>Maple Ridge</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>revolutionbball@gmail.com</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>https://www.revolutionbasketballclub.com/</t>
@@ -24968,13 +24031,11 @@
           <t>Mission</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>info@missionbasketball.ca</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>https://missionbasketball.ca/</t>
@@ -24992,8 +24053,6 @@
           <t>Nanaimo</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>Chris Russell — Director (15+ years coaching experience)</t>
@@ -25016,7 +24075,6 @@
           <t>Nanaimo</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>chrisjoseph12@gmail.com</t>
@@ -25027,7 +24085,6 @@
           <t>Chris Joseph — Basketball BC registry contact (role not stated)</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -25040,7 +24097,6 @@
           <t>Nanaimo</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>info@islandswish.com</t>
@@ -25100,7 +24156,6 @@
           <t>Nelson</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>nelsonyouthbasketball@gmail.com</t>
@@ -25128,7 +24183,6 @@
           <t>New Westminster</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>info@newwestbasketball.com</t>
@@ -25166,7 +24220,6 @@
           <t>info@3dbasketball.net</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>https://www.3dbasketball.net</t>
@@ -25184,13 +24237,11 @@
           <t>North Vancouver</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>info@bcunitedbasketball.com</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>https://www.bcunitedbasketball.com</t>
@@ -25282,7 +24333,6 @@
           <t>info@northshorebasketballacademy.com</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>https://www.northshorebasketballacademy.com/</t>
@@ -25310,7 +24360,6 @@
           <t>info@seymourbasketball.com</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>seymourbasketball.com</t>
@@ -25328,13 +24377,11 @@
           <t>North Vancouver</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>splashbrothersbasketball1@gmail.com</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>https://www.splashbballbc.com</t>
@@ -25448,8 +24495,6 @@
           <t>North Vancouver</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Ransford Brempong, Owner/Director/Head Coach</t>
@@ -25472,7 +24517,6 @@
           <t>North Vancouver (per basketball604; Basketball BC registry lists it in Thompson-Okanagan)</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>Kaitlyn@newheightsbasketball.com</t>
@@ -25564,7 +24608,6 @@
           <t>Penticton</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>jaiveer17@icloud.com</t>
@@ -25575,7 +24618,6 @@
           <t>Jaiveer Dhillon — Founder/coach (19 years old, founded as a player-turned-coach)</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -25588,13 +24630,11 @@
           <t>Pitt Meadows</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>nsattackathletics@gmail.com</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>https://www.northsideattack.com/</t>
@@ -25676,7 +24716,6 @@
           <t>Port Coquitlam</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>sassanrakhshani@yahoo.com</t>
@@ -25768,7 +24807,6 @@
           <t>Prince George</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>pgminorbasketball@gmail.com</t>
@@ -25796,7 +24834,6 @@
           <t>Prince George (HQ) + Kamloops division</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>hoops@northernbounce.com</t>
@@ -25856,14 +24893,11 @@
           <t>Quesnel</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>Sean Cunningham — Basketball BC registry contact</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -25908,13 +24942,11 @@
           <t>Richmond</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>cmntyelite@gmail.com</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>https://www.community-elite.com/</t>
@@ -25932,7 +24964,6 @@
           <t>Richmond</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>landondy_11@yahoo.com</t>
@@ -25960,8 +24991,6 @@
           <t>Richmond</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Angelo Wilchcombe, Owner</t>
@@ -25984,13 +25013,11 @@
           <t>Richmond</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>playmakersbballtraining@gmail.com</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>https://playmakersbball.com</t>
@@ -26045,8 +25072,6 @@
           <t>604-347-5151</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>https://www.facebook.com/ShootingStarsBall/</t>
@@ -26064,13 +25089,11 @@
           <t>Richmond</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>WRSummerslam@Richmond.ca</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>https://www.westrichmondsummerslam.com/</t>
@@ -26088,7 +25111,6 @@
           <t>Saanich (Royal Oak)</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>rebelsrebelles@gmail.com</t>
@@ -26116,7 +25138,6 @@
           <t>Salmon Arm</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>shuswaphoops2023@gmail.com</t>
@@ -26144,7 +25165,6 @@
           <t>Salt Spring Island</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>saltspringbasketball@gmail.com</t>
@@ -26172,7 +25192,6 @@
           <t>Smithers</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>clubbasketballbv@gmail.com</t>
@@ -26205,8 +25224,6 @@
           <t>604-907-2024</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>https://hustlebasketball.ca/</t>
@@ -26224,7 +25241,6 @@
           <t>Squamish</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>info@hoopreel.com</t>
@@ -26252,7 +25268,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>info@athelitebasketball.com</t>
@@ -26285,8 +25300,6 @@
           <t>778-591-3660</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>http://www.bcprep.com</t>
@@ -26314,7 +25327,6 @@
           <t>info@bcprep.com</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>https://bcprep.com/</t>
@@ -26337,7 +25349,6 @@
           <t>604-670-4340</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>Pasha Bains (co-founder; ex-NCAA D1 Clemson) and Chad Clifford (co-founder; ex-NCAA D1 St. Francis PA)</t>
@@ -26392,8 +25403,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>Elle Kerfoot, Owner</t>
@@ -26416,7 +25425,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>reid_g@surreyschools.ca</t>
@@ -26427,7 +25435,6 @@
           <t>Greg Reid — Basketball BC registry contact</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -26472,14 +25479,11 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>Elliot Mason, Head Coach</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -26502,7 +25506,6 @@
           <t>basketballfv@gmail.com</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>https://sites.google.com/site/fvbasketball/</t>
@@ -26520,8 +25523,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>Jun Labrador, Founder/Coach</t>
@@ -26544,7 +25545,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>info@nextgenerationathletics.ca</t>
@@ -26646,7 +25646,6 @@
           <t>info.showtimebasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>https://www.showtimeacademy.net</t>
@@ -26664,8 +25663,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>Steve Beauchamp — lead coach/organizer</t>
@@ -26698,7 +25695,6 @@
           <t>spottersbball@hotmail.com</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>https://www.facebook.com/spottersbball</t>
@@ -26716,7 +25712,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>Bsingh.aloha@outlook.com</t>
@@ -26727,7 +25722,6 @@
           <t>Bob Singh — Basketball BC registry contact</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -26740,13 +25734,11 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>info.surreyrebelsbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>https://www.surreyrebelsbasketball.com/</t>
@@ -26796,7 +25788,6 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>info@vancouversportsclub.ca</t>
@@ -26824,13 +25815,11 @@
           <t>Surrey</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>info@westcoastbasketball.com</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>https://www.westcoastbasketball.com</t>
@@ -26880,7 +25869,6 @@
           <t>Surrey (South Surrey / White Rock)</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>elevateyourgame.info@gmail.com</t>
@@ -26913,7 +25901,6 @@
           <t>250-635-6531 ext 8017</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>Joe Dominguez — program contact (per City of Terrace sports club directory)</t>
@@ -26941,7 +25928,6 @@
           <t>778.835.3632</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>Mark Starkey — Founder</t>
@@ -26964,7 +25950,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>cmntyelite@gmail.com</t>
@@ -27024,8 +26009,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>Brodan Thiel — Co-Founder; Louis Johnson — Co-Founder</t>
@@ -27048,7 +26031,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>coaches@formbasketball.com</t>
@@ -27076,7 +26058,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>team@finishstrongbasketball.ca</t>
@@ -27104,7 +26085,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>futurebouncebasketball@gmail.com</t>
@@ -27132,7 +26112,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>rpennington.basketball@gmail.com</t>
@@ -27143,7 +26122,6 @@
           <t>Rodney Pennington — Basketball BC registry contact</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -27188,7 +26166,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>journeybasketball2020@gmail.com</t>
@@ -27290,7 +26267,6 @@
           <t>info.recreation@ubc.ca</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>https://ysbc.bms-1.com</t>
@@ -27308,7 +26284,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>info@nighthoops.ca</t>
@@ -27336,8 +26311,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>Warren Liang (Founder)</t>
@@ -27552,7 +26525,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
           <t>vancouveracesbballclub@gmail.com</t>
@@ -27590,7 +26562,6 @@
           <t>info@vancouvereagles.com</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>https://vancouvereagles.com/</t>
@@ -27608,7 +26579,6 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>info@vgba.ca</t>
@@ -27732,13 +26702,11 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>yuvasc2018@gmail.com</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>https://www.facebook.com/vancitysc/</t>
@@ -27756,8 +26724,6 @@
           <t>Vancouver Island (city unconfirmed)</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>Michael Smith — coach/operator</t>
@@ -27780,7 +26746,6 @@
           <t>Vancouver Island (city unconfirmed)</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>thewatchmanacademymentorship@gmail.com</t>
@@ -27791,7 +26756,6 @@
           <t>Ayodeji Ipaye — Basketball BC registry contact (role not stated)</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -27809,7 +26773,6 @@
           <t>(778) 240-5370</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>"Coach On" — founder (started the program so his daughters would have a team; full name not published)</t>
@@ -27864,7 +26827,6 @@
           <t>Vernon</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
           <t>tayahoops@gmail.com</t>
@@ -27892,8 +26854,6 @@
           <t>Vernon</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>Andy Collins and Mark Zaino — co-founders (per Vernon Morning Star)</t>
@@ -27921,7 +26881,6 @@
           <t>1-677-124-44227</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>Landry Ndayitwayeko, Yassine Ghomari, Mitch Goodwin — Co-Founders/Directors/Head Coaches</t>
@@ -27944,8 +26903,6 @@
           <t>Vernon / Lake Country</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>Ed Lefurgy — Coach/operator (with Steph Lefurgy)</t>
@@ -27968,7 +26925,6 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
           <t>carnarvonvpbasketball@gmail.com</t>
@@ -28001,7 +26957,6 @@
           <t>(250) 592-4038</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>Eli Pasquale — founder (namesake, ex-UVic star)</t>
@@ -28024,7 +26979,6 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>Info@flightbasketball.ca</t>
@@ -28052,13 +27006,11 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
           <t>academy@gryphonsbasketball.net</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>https://www.gryphonsbasketball.net</t>
@@ -28081,7 +27033,6 @@
           <t>(250) 999-9380</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
           <t>Joosep Pokla — Head Coach &amp; Program Manager; Kevin "Kit" Fu — Head Coach (owner not published)</t>
@@ -28104,7 +27055,6 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>hello@rexsports.ca</t>
@@ -28132,8 +27082,6 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>Brett Westcott — President (directors: Gary Mols, Bryn Barker, Dallas Lansdell)</t>
@@ -28188,8 +27136,6 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>'Coach Hutch' — longtime leader (reported recently retired)</t>
@@ -28212,7 +27158,6 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>viccityhoops@gmail.com</t>
@@ -28240,13 +27185,11 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>office@vichowlers.ca</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>https://vichowlers.ca/</t>
@@ -28264,7 +27207,6 @@
           <t>Victoria</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
           <t>cve@uvic.ca</t>
@@ -28324,7 +27266,6 @@
           <t>West Kelowna</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
           <t>westkhoops@gmail.com</t>
@@ -28384,14 +27325,11 @@
           <t>Williams Lake</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>Jeremy LaBelle — head coach</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -28429,4 +27367,356 @@
   <autoFilter ref="A1:F194"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Teams counted (directional)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Breakdown (league=teams)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Prince George Minor Basketball Association</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Prince George Minor Basketball Associa=19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DRIVE Basketball League</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DRIVE Basketball League (DBL) + in-hou=12; DRIVE Basketball League (DBL) + in-hou=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bay Nation</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>V&amp;DABA Night League (Victoria and Dist=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Westshore Basketball (WS)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>V&amp;DABA Night League (Victoria and Dist=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SMUS (St. Michaels University School)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>V&amp;DABA Night League (Victoria and Dist=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Carnarvon Ball Club</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>V&amp;DABA Night League (Victoria and Dist=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Warriors</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>V&amp;DABA Night League (Victoria and Dist=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Flight</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>V&amp;DABA Night League (Victoria and Dist=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>V&amp;DABA Night League (Victoria and Dist=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Grind</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>V&amp;DABA Night League (Victoria and Dist=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Rebelles</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>V&amp;DABA Night League (Victoria and Dist=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SPABA (Saanich Peninsula Amateur Basketball Association)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>V&amp;DABA Night League (Victoria and Dist=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>V&amp;DABA Night League (Victoria and Dist=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>The Home Court</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Vancouver Eagles Youth Basketball (SNY=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Capital City Hoopsters</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>V&amp;DABA Night League (Victoria and Dist=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Thunder Nation</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>V&amp;DABA Night League (Victoria and Dist=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>The Angels</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>V&amp;DABA Night League (Victoria and Dist=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Alamat</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Vancouver Eagles Youth Basketball (SNY=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Raincity</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Vancouver Eagles Youth Basketball (SNY=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>South Delta Basketball Association</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Vancouver Eagles Youth Basketball (SNY=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Vancouver Eagles Youth Basketball Club</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Vancouver Eagles Youth Basketball (SNY=1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C22"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/research/provinces/SportsHub-British-Columbia.xlsx
+++ b/docs/research/provinces/SportsHub-British-Columbia.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$Q$230</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$199</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$194</definedName>
@@ -65,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P230"/>
+  <dimension ref="A1:Q230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -454,6 +455,7 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,6 +539,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3554,6 +3561,9 @@
           <t>Affiliated with Basketball BC | Also listed as: South Delta Basketball Association | enriched 2026-07-18</t>
         </is>
       </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8139,6 +8149,9 @@
           <t>Partnership with UNBC Timberwolves (halftime performances)</t>
         </is>
       </c>
+      <c r="Q117" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9759,6 +9772,9 @@
           <t>Largest private operator in region; since 2004</t>
         </is>
       </c>
+      <c r="Q142" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13114,6 +13130,9 @@
           <t>One of the largest Vancouver youth programs; operator of its own leagues</t>
         </is>
       </c>
+      <c r="Q197" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -14089,6 +14108,9 @@
           <t>No independent web presence found; evidence limited to V&amp;DABA member list.</t>
         </is>
       </c>
+      <c r="Q212" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -14166,6 +14188,9 @@
           <t>Basketball BC 2025-26 member club (listed under both Fraser Valley and Vancouver Island-Central Coast headings; club is Victoria-based). | Also listed as: Carnarvon Ball Club (Basketball)</t>
         </is>
       </c>
+      <c r="Q213" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -14737,6 +14762,9 @@
           <t>Thin web presence; status after Coach Hutch's retirement worth confirming by outreach.</t>
         </is>
       </c>
+      <c r="Q221" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -15337,7 +15365,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P230"/>
+  <autoFilter ref="A1:Q230"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
